--- a/artfynd/A 29209-2024 artfynd.xlsx
+++ b/artfynd/A 29209-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY27"/>
+  <dimension ref="A1:AY32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111465711</v>
+        <v>111465732</v>
       </c>
       <c r="B2" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,21 +686,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -716,10 +711,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>554598.0284524948</v>
+        <v>554609</v>
       </c>
       <c r="R2" t="n">
-        <v>7003691.535042655</v>
+        <v>7003684</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -749,24 +744,9 @@
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2023-08-14</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>På björk</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -793,15 +773,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>111466357</v>
+        <v>111465831</v>
       </c>
       <c r="B3" t="n">
-        <v>56543</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92208</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -809,40 +784,35 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fomitopsis rosea</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Alb. &amp; Schwein.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>stationär</t>
-        </is>
-      </c>
       <c r="P3" t="inlineStr">
         <is>
           <t>Gräsmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>554503.6495146402</v>
+        <v>554595</v>
       </c>
       <c r="R3" t="n">
-        <v>7003651.521970394</v>
+        <v>7003672</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -872,24 +842,9 @@
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>13:33</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2023-08-14</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>13:33</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>Familj</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -916,15 +871,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>111472260</v>
+        <v>111465625</v>
       </c>
       <c r="B4" t="n">
-        <v>77267</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -932,21 +882,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6446</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -957,10 +907,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>554682.6075079201</v>
+        <v>554621</v>
       </c>
       <c r="R4" t="n">
-        <v>7003561.425211067</v>
+        <v>7003710</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -990,19 +940,9 @@
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>15:49</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2023-08-14</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>15:49</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1029,37 +969,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>111466325</v>
+        <v>111465834</v>
       </c>
       <c r="B5" t="n">
-        <v>78536</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91909</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>229497</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Korallblylav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Parmeliella triptophylla</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Müll.Arg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1070,10 +1005,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>554517.0769914992</v>
+        <v>554595</v>
       </c>
       <c r="R5" t="n">
-        <v>7003633.667468631</v>
+        <v>7003672</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1103,19 +1038,9 @@
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>13:33</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-08-14</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>13:33</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1142,37 +1067,32 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>111466223</v>
+        <v>111466925</v>
       </c>
       <c r="B6" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92369</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220787</v>
+        <v>1209</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rynkskinn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hermanssonia centrifuga</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(P. Karst.) Zmitr.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1183,10 +1103,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>554519.5559518669</v>
+        <v>554505</v>
       </c>
       <c r="R6" t="n">
-        <v>7003647.721871981</v>
+        <v>7003585</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1216,19 +1136,9 @@
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>13:33</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-08-14</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>13:33</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1255,37 +1165,32 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>111465625</v>
+        <v>111465528</v>
       </c>
       <c r="B7" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1296,10 +1201,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>554620.7857306475</v>
+        <v>554642</v>
       </c>
       <c r="R7" t="n">
-        <v>7003710.903772585</v>
+        <v>7003761</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1329,19 +1234,9 @@
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>2023-08-14</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1368,15 +1263,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>111465972</v>
+        <v>111465573</v>
       </c>
       <c r="B8" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1384,21 +1274,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1409,10 +1299,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>554571.2772579535</v>
+        <v>554566</v>
       </c>
       <c r="R8" t="n">
-        <v>7003694.247686354</v>
+        <v>7003716</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1442,19 +1332,9 @@
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>13:13</t>
-        </is>
-      </c>
       <c r="AA8" t="inlineStr">
         <is>
           <t>2023-08-14</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>13:13</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1481,37 +1361,32 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>111465875</v>
+        <v>111465666</v>
       </c>
       <c r="B9" t="n">
-        <v>96368</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>221952</v>
+        <v>6425</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1522,10 +1397,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>554571.5288519162</v>
+        <v>554601</v>
       </c>
       <c r="R9" t="n">
-        <v>7003679.3354731</v>
+        <v>7003707</v>
       </c>
       <c r="S9" t="n">
         <v>25</v>
@@ -1555,19 +1430,14 @@
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA9" t="inlineStr">
         <is>
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC9" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1594,19 +1464,14 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111465666</v>
+        <v>111465734</v>
       </c>
       <c r="B10" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
@@ -1635,10 +1500,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>554600.9442600238</v>
+        <v>554609</v>
       </c>
       <c r="R10" t="n">
-        <v>7003706.50066955</v>
+        <v>7003684</v>
       </c>
       <c r="S10" t="n">
         <v>25</v>
@@ -1668,24 +1533,9 @@
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA10" t="inlineStr">
         <is>
           <t>2023-08-14</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC10" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1712,37 +1562,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111465831</v>
+        <v>111465802</v>
       </c>
       <c r="B11" t="n">
-        <v>89686</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1753,10 +1598,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>554595.6337710663</v>
+        <v>554587</v>
       </c>
       <c r="R11" t="n">
-        <v>7003672.510005065</v>
+        <v>7003690</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1786,19 +1631,14 @@
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA11" t="inlineStr">
         <is>
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC11" t="inlineStr">
+        <is>
+          <t>Rikligt, även på tallstammar</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1825,15 +1665,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>111466143</v>
+        <v>111465995</v>
       </c>
       <c r="B12" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1841,21 +1676,21 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1866,10 +1701,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>554532.5492710491</v>
+        <v>554561</v>
       </c>
       <c r="R12" t="n">
-        <v>7003655.625220859</v>
+        <v>7003683</v>
       </c>
       <c r="S12" t="n">
         <v>25</v>
@@ -1901,7 +1736,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1911,7 +1746,12 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:26</t>
+          <t>13:13</t>
+        </is>
+      </c>
+      <c r="AC12" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1938,19 +1778,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>111465995</v>
+        <v>111467978</v>
       </c>
       <c r="B13" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1979,10 +1814,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>554560.1475693721</v>
+        <v>554462</v>
       </c>
       <c r="R13" t="n">
-        <v>7003683.211603408</v>
+        <v>7003581</v>
       </c>
       <c r="S13" t="n">
         <v>25</v>
@@ -2014,7 +1849,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2024,12 +1859,12 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>13:13</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2056,19 +1891,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>111465528</v>
+        <v>111472146</v>
       </c>
       <c r="B14" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -2097,10 +1927,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>554641.2289003483</v>
+        <v>554693</v>
       </c>
       <c r="R14" t="n">
-        <v>7003760.065867206</v>
+        <v>7003552</v>
       </c>
       <c r="S14" t="n">
         <v>25</v>
@@ -2132,7 +1962,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2142,7 +1972,12 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>15:49</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2169,37 +2004,32 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>111472311</v>
+        <v>111472260</v>
       </c>
       <c r="B15" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79084</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
@@ -2210,10 +2040,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>554674.6930893421</v>
+        <v>554683</v>
       </c>
       <c r="R15" t="n">
-        <v>7003574.400324564</v>
+        <v>7003562</v>
       </c>
       <c r="S15" t="n">
         <v>25</v>
@@ -2245,7 +2075,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2255,7 +2085,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>16:29</t>
+          <t>15:49</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2282,37 +2112,32 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>111466045</v>
+        <v>111465509</v>
       </c>
       <c r="B16" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
@@ -2323,10 +2148,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>554562.6006728654</v>
+        <v>554695</v>
       </c>
       <c r="R16" t="n">
-        <v>7003671.952605859</v>
+        <v>7003796</v>
       </c>
       <c r="S16" t="n">
         <v>25</v>
@@ -2356,19 +2181,14 @@
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>13:19</t>
-        </is>
-      </c>
       <c r="AA16" t="inlineStr">
         <is>
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>13:19</t>
+      <c r="AC16" t="inlineStr">
+        <is>
+          <t>På grov sälg</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2395,37 +2215,32 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>111466925</v>
+        <v>111465711</v>
       </c>
       <c r="B17" t="n">
-        <v>89845</v>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>1209</v>
+        <v>6458</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rynkskinn</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Phlebia centrifuga</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
@@ -2436,10 +2251,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>554504.308730279</v>
+        <v>554598</v>
       </c>
       <c r="R17" t="n">
-        <v>7003585.537716132</v>
+        <v>7003692</v>
       </c>
       <c r="S17" t="n">
         <v>25</v>
@@ -2469,19 +2284,14 @@
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA17" t="inlineStr">
         <is>
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>00:00</t>
+      <c r="AC17" t="inlineStr">
+        <is>
+          <t>På björk</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2511,12 +2321,7 @@
         <v>111466324</v>
       </c>
       <c r="B18" t="n">
-        <v>78578</v>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2549,10 +2354,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>554517.0769914992</v>
+        <v>554517</v>
       </c>
       <c r="R18" t="n">
-        <v>7003633.667468631</v>
+        <v>7003634</v>
       </c>
       <c r="S18" t="n">
         <v>25</v>
@@ -2621,32 +2426,27 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>111472146</v>
+        <v>111466291</v>
       </c>
       <c r="B19" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80467</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>6463</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bårdlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma parile</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2662,10 +2462,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>554692.7311306486</v>
+        <v>554531</v>
       </c>
       <c r="R19" t="n">
-        <v>7003551.651650672</v>
+        <v>7003642</v>
       </c>
       <c r="S19" t="n">
         <v>25</v>
@@ -2697,7 +2497,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:49</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2707,12 +2507,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:49</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2739,51 +2534,51 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>111466291</v>
+        <v>111466357</v>
       </c>
       <c r="B20" t="n">
-        <v>78611</v>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58114</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6463</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bårdlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Nephroma parile</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="K20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>stationär</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Gräsmyrbäcken, Jmt</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>554531.8804235036</v>
+        <v>554504</v>
       </c>
       <c r="R20" t="n">
-        <v>7003641.601355875</v>
+        <v>7003652</v>
       </c>
       <c r="S20" t="n">
         <v>25</v>
@@ -2826,6 +2621,11 @@
       <c r="AB20" t="inlineStr">
         <is>
           <t>13:33</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr">
+        <is>
+          <t>Familj</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2852,15 +2652,10 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>111466448</v>
+        <v>111465554</v>
       </c>
       <c r="B21" t="n">
-        <v>95538</v>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99035</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2868,21 +2663,21 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>221941</v>
+        <v>219790</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Plattlummer</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Lycopodium complanatum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
@@ -2893,10 +2688,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>554497.9876700568</v>
+        <v>554567</v>
       </c>
       <c r="R21" t="n">
-        <v>7003638.318009931</v>
+        <v>7003726</v>
       </c>
       <c r="S21" t="n">
         <v>25</v>
@@ -2926,19 +2721,9 @@
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA21" t="inlineStr">
         <is>
           <t>2023-08-14</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2965,37 +2750,32 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>111465802</v>
+        <v>111465972</v>
       </c>
       <c r="B22" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
@@ -3006,10 +2786,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>554587.1835726696</v>
+        <v>554571</v>
       </c>
       <c r="R22" t="n">
-        <v>7003690.447973201</v>
+        <v>7003694</v>
       </c>
       <c r="S22" t="n">
         <v>25</v>
@@ -3041,7 +2821,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3051,12 +2831,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr">
-        <is>
-          <t>Rikligt, även på tallstammar</t>
+          <t>13:13</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3083,15 +2858,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>111472405</v>
+        <v>111466045</v>
       </c>
       <c r="B23" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3124,10 +2894,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>554669.2876365461</v>
+        <v>554563</v>
       </c>
       <c r="R23" t="n">
-        <v>7003599.622546442</v>
+        <v>7003672</v>
       </c>
       <c r="S23" t="n">
         <v>25</v>
@@ -3159,7 +2929,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3169,7 +2939,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3196,37 +2966,32 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>111465834</v>
+        <v>111466143</v>
       </c>
       <c r="B24" t="n">
-        <v>89405</v>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3237,10 +3002,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>554595.6337710663</v>
+        <v>554533</v>
       </c>
       <c r="R24" t="n">
-        <v>7003672.510005065</v>
+        <v>7003656</v>
       </c>
       <c r="S24" t="n">
         <v>25</v>
@@ -3272,7 +3037,7 @@
       </c>
       <c r="Z24" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AA24" t="inlineStr">
@@ -3282,7 +3047,7 @@
       </c>
       <c r="AB24" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:26</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3309,37 +3074,32 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>111465732</v>
+        <v>111466223</v>
       </c>
       <c r="B25" t="n">
-        <v>89686</v>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3350,10 +3110,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>554609.4631597863</v>
+        <v>554520</v>
       </c>
       <c r="R25" t="n">
-        <v>7003684.495857589</v>
+        <v>7003647</v>
       </c>
       <c r="S25" t="n">
         <v>25</v>
@@ -3385,7 +3145,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3395,7 +3155,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>13:33</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3425,12 +3185,7 @@
         <v>111466849</v>
       </c>
       <c r="B26" t="n">
-        <v>96348</v>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3463,10 +3218,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>554499.5322661656</v>
+        <v>554500</v>
       </c>
       <c r="R26" t="n">
-        <v>7003600.374111877</v>
+        <v>7003600</v>
       </c>
       <c r="S26" t="n">
         <v>25</v>
@@ -3496,19 +3251,9 @@
           <t>2023-08-14</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2023-08-14</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3535,37 +3280,32 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>111465734</v>
+        <v>111467001</v>
       </c>
       <c r="B27" t="n">
-        <v>77515</v>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99118</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3576,10 +3316,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>554609.4631597863</v>
+        <v>554493</v>
       </c>
       <c r="R27" t="n">
-        <v>7003684.495857589</v>
+        <v>7003576</v>
       </c>
       <c r="S27" t="n">
         <v>25</v>
@@ -3611,7 +3351,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3621,7 +3361,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>14:05</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3645,6 +3385,526 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>111472311</v>
+      </c>
+      <c r="B28" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Gräsmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>554674</v>
+      </c>
+      <c r="R28" t="n">
+        <v>7003574</v>
+      </c>
+      <c r="S28" t="n">
+        <v>25</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>16:29</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>111472405</v>
+      </c>
+      <c r="B29" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Gräsmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>554669</v>
+      </c>
+      <c r="R29" t="n">
+        <v>7003599</v>
+      </c>
+      <c r="S29" t="n">
+        <v>25</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>111466448</v>
+      </c>
+      <c r="B30" t="n">
+        <v>97989</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>221941</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Plattlummer</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Lycopodium complanatum</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Gräsmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>554498</v>
+      </c>
+      <c r="R30" t="n">
+        <v>7003639</v>
+      </c>
+      <c r="S30" t="n">
+        <v>25</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>111465875</v>
+      </c>
+      <c r="B31" t="n">
+        <v>99140</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>221952</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Spindelblomster</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Neottia cordata</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Gräsmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>554571</v>
+      </c>
+      <c r="R31" t="n">
+        <v>7003679</v>
+      </c>
+      <c r="S31" t="n">
+        <v>25</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>111466325</v>
+      </c>
+      <c r="B32" t="n">
+        <v>80392</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>229497</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Korallblylav</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Parmeliella triptophylla</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(Ach.) Müll.Arg.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Gräsmyrbäcken, Jmt</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>554517</v>
+      </c>
+      <c r="R32" t="n">
+        <v>7003634</v>
+      </c>
+      <c r="S32" t="n">
+        <v>25</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Ragunda</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2023-08-14</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>13:33</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Erland Lindblad</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 29209-2024 artfynd.xlsx
+++ b/artfynd/A 29209-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY32"/>
+  <dimension ref="A1:AZ32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -770,6 +775,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111465732</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -868,6 +878,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111465831</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -966,6 +981,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111465625</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1064,6 +1084,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111465834</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1162,6 +1187,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111466925</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1260,6 +1290,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111465528</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1358,6 +1393,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111465573</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1461,6 +1501,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111465666</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1559,6 +1604,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111465734</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1662,6 +1712,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111465802</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1775,6 +1830,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111465995</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1888,6 +1948,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111467978</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2001,6 +2066,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111472146</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2109,6 +2179,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111472260</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2212,6 +2287,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111465509</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2315,6 +2395,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111465711</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2423,6 +2508,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111466324</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2531,6 +2621,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111466291</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2649,6 +2744,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111466357</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2747,6 +2847,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111465554</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2855,6 +2960,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111465972</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2963,6 +3073,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111466045</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3071,6 +3186,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111466143</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3179,6 +3299,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111466223</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3277,6 +3402,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111466849</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3385,6 +3515,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111467001</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3493,6 +3628,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111472311</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3601,6 +3741,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111472405</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3699,6 +3844,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111466448</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3797,6 +3947,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111465875</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3905,8 +4060,46 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111466325</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>